--- a/artfynd/A 7040-2026 artfynd.xlsx
+++ b/artfynd/A 7040-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131578233</v>
       </c>
       <c r="B2" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>131578158</v>
       </c>
       <c r="B3" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>131577999</v>
       </c>
       <c r="B4" t="n">
-        <v>58051</v>
+        <v>58057</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>131578289</v>
       </c>
       <c r="B5" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>131578360</v>
       </c>
       <c r="B6" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>131578341</v>
       </c>
       <c r="B7" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>131578316</v>
       </c>
       <c r="B8" t="n">
-        <v>58051</v>
+        <v>58057</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>131577884</v>
       </c>
       <c r="B9" t="n">
-        <v>57080</v>
+        <v>57086</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 7040-2026 artfynd.xlsx
+++ b/artfynd/A 7040-2026 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>131578158</v>
       </c>
       <c r="B3" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>131578289</v>
       </c>
       <c r="B5" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>131578341</v>
       </c>
       <c r="B7" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 7040-2026 artfynd.xlsx
+++ b/artfynd/A 7040-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131578233</v>
       </c>
       <c r="B2" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>131578158</v>
       </c>
       <c r="B3" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>131577999</v>
       </c>
       <c r="B4" t="n">
-        <v>58057</v>
+        <v>58058</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>131578289</v>
       </c>
       <c r="B5" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>131578360</v>
       </c>
       <c r="B6" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>131578341</v>
       </c>
       <c r="B7" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>131578316</v>
       </c>
       <c r="B8" t="n">
-        <v>58057</v>
+        <v>58058</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>131577884</v>
       </c>
       <c r="B9" t="n">
-        <v>57086</v>
+        <v>57087</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 7040-2026 artfynd.xlsx
+++ b/artfynd/A 7040-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131578233</v>
       </c>
       <c r="B2" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>131578158</v>
       </c>
       <c r="B3" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>131577999</v>
       </c>
       <c r="B4" t="n">
-        <v>58058</v>
+        <v>58061</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>131578289</v>
       </c>
       <c r="B5" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>131578360</v>
       </c>
       <c r="B6" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>131578341</v>
       </c>
       <c r="B7" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>131578316</v>
       </c>
       <c r="B8" t="n">
-        <v>58058</v>
+        <v>58061</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>131577884</v>
       </c>
       <c r="B9" t="n">
-        <v>57087</v>
+        <v>57090</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 7040-2026 artfynd.xlsx
+++ b/artfynd/A 7040-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131578233</v>
       </c>
       <c r="B2" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>131578158</v>
       </c>
       <c r="B3" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>131577999</v>
       </c>
       <c r="B4" t="n">
-        <v>58061</v>
+        <v>58063</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>131578289</v>
       </c>
       <c r="B5" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>131578360</v>
       </c>
       <c r="B6" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>131578341</v>
       </c>
       <c r="B7" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>131578316</v>
       </c>
       <c r="B8" t="n">
-        <v>58061</v>
+        <v>58063</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>131577884</v>
       </c>
       <c r="B9" t="n">
-        <v>57090</v>
+        <v>57092</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
